--- a/144/DQ Templates and Instructions/Topic 3 DQ 1/Topic 3 DQ 1.xlsx
+++ b/144/DQ Templates and Instructions/Topic 3 DQ 1/Topic 3 DQ 1.xlsx
@@ -1,25 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://gcumail.sharepoint.com/sites/MathematicsProgramFacultyStaff-MATOFTF/Shared Documents/MATOFTF/ALEKS/DQ Templates and Instructions/Topic 3 DQ 1/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="363" documentId="8_{C5702531-EDB5-4409-B5CA-675AC228E6F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E37C3A3E-D2BC-4E5E-95F2-8C02AF2E9255}"/>
+  <xr:revisionPtr revIDLastSave="378" documentId="8_{C5702531-EDB5-4409-B5CA-675AC228E6F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DCE310B7-0079-4DBA-926B-2A126F04A064}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{4FCF7FA6-22BB-4545-AB27-D5B8AACA448D}"/>
   </bookViews>
   <sheets>
     <sheet name="Goals and Instructions" sheetId="6" r:id="rId1"/>
     <sheet name="Financial" sheetId="1" r:id="rId2"/>
-    <sheet name="Random" sheetId="4" state="hidden" r:id="rId3"/>
-    <sheet name="Solutions" sheetId="2" state="hidden" r:id="rId4"/>
-    <sheet name="Sheet1" sheetId="5" state="hidden" r:id="rId5"/>
+    <sheet name="Users" sheetId="7" state="hidden" r:id="rId3"/>
+    <sheet name="Random" sheetId="4" state="hidden" r:id="rId4"/>
+    <sheet name="Solutions" sheetId="2" state="hidden" r:id="rId5"/>
+    <sheet name="Sheet1" sheetId="5" state="hidden" r:id="rId6"/>
   </sheets>
-  <calcPr calcId="191028"/>
+  <calcPr calcId="191028" iterate="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -58,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="162" uniqueCount="100">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="163" uniqueCount="102">
   <si>
     <t>Excel Skills Learned</t>
   </si>
@@ -379,6 +380,12 @@
   <si>
     <t xml:space="preserve">Enter you name here ⇒ </t>
   </si>
+  <si>
+    <t>Names</t>
+  </si>
+  <si>
+    <t>Reset</t>
+  </si>
 </sst>
 </file>
 
@@ -387,7 +394,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.00"/>
   </numFmts>
-  <fonts count="18">
+  <fonts count="17">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -508,12 +515,6 @@
       <name val="Baguet Script"/>
     </font>
     <font>
-      <sz val="9"/>
-      <color indexed="81"/>
-      <name val="Tahoma"/>
-      <charset val="1"/>
-    </font>
-    <font>
       <b/>
       <sz val="18"/>
       <color theme="10"/>
@@ -522,7 +523,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="11">
+  <fills count="12">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -580,6 +581,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="0" tint="-4.9989318521683403E-2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="2" tint="-0.249977111117893"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1240,7 +1247,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="208">
+  <cellXfs count="207">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1357,13 +1364,10 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyProtection="1">
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" applyProtection="1">
       <alignment vertical="center"/>
       <protection locked="0"/>
     </xf>
@@ -1377,14 +1381,11 @@
       <alignment horizontal="center"/>
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <protection hidden="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="41" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" applyProtection="1">
       <alignment vertical="center"/>
       <protection hidden="1"/>
     </xf>
@@ -1428,9 +1429,6 @@
       <protection hidden="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyProtection="1">
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyProtection="1">
@@ -1535,6 +1533,66 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="37" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="38" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="39" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="32" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="36" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="33" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="30" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="40" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="7" borderId="37" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="7" borderId="38" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="7" borderId="39" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="7" borderId="37" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="7" borderId="38" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="7" borderId="39" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
     <xf numFmtId="164" fontId="0" fillId="7" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
@@ -1547,6 +1605,162 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="31" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" indent="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="44" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" indent="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="42" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="45" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="42" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" indent="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="45" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" indent="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="43" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="46" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="10" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="10" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="10" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="10" borderId="47" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="10" borderId="48" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
     <xf numFmtId="0" fontId="13" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
       <protection hidden="1"/>
@@ -1571,77 +1785,17 @@
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-      <protection hidden="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="37" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
+      <alignment horizontal="center" vertical="center"/>
       <protection hidden="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="38" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
+      <alignment horizontal="center" vertical="center"/>
       <protection hidden="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="39" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="37" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="38" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="39" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="7" borderId="37" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="7" borderId="38" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="7" borderId="39" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="7" borderId="37" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="7" borderId="38" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="7" borderId="39" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
@@ -1655,167 +1809,128 @@
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="7" borderId="37" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="7" borderId="38" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="7" borderId="39" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="7" borderId="37" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="7" borderId="38" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="7" borderId="39" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="30" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="40" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="26" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="24" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="30" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="40" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="31" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" indent="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="44" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" indent="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="42" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="45" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="42" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" indent="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="45" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" indent="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="43" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="46" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="10" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="10" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="10" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="32" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="32" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="36" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="36" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="33" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="33" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-      <protection hidden="1"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="7" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1844,125 +1959,16 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="39" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="7" borderId="37" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="7" borderId="38" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="7" borderId="39" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="7" borderId="37" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="7" borderId="38" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="7" borderId="39" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="26" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="24" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="32" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="36" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="33" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="30" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="40" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="10" borderId="47" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="10" borderId="48" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="25" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -2832,53 +2838,53 @@
       <c r="B2" s="21" t="s">
         <v>0</v>
       </c>
-      <c r="D2" s="79" t="s">
+      <c r="D2" s="76" t="s">
         <v>1</v>
       </c>
-      <c r="E2" s="80"/>
-      <c r="F2" s="80"/>
-      <c r="G2" s="80"/>
-      <c r="H2" s="80"/>
-      <c r="I2" s="81"/>
+      <c r="E2" s="77"/>
+      <c r="F2" s="77"/>
+      <c r="G2" s="77"/>
+      <c r="H2" s="77"/>
+      <c r="I2" s="78"/>
     </row>
     <row r="3" spans="2:9">
       <c r="B3" t="s">
         <v>2</v>
       </c>
-      <c r="D3" s="82"/>
-      <c r="E3" s="83"/>
-      <c r="F3" s="83"/>
-      <c r="G3" s="83"/>
-      <c r="H3" s="83"/>
-      <c r="I3" s="84"/>
+      <c r="D3" s="79"/>
+      <c r="E3" s="80"/>
+      <c r="F3" s="80"/>
+      <c r="G3" s="80"/>
+      <c r="H3" s="80"/>
+      <c r="I3" s="81"/>
     </row>
     <row r="4" spans="2:9" ht="30">
       <c r="B4" s="23" t="s">
         <v>86</v>
       </c>
-      <c r="D4" s="82"/>
-      <c r="E4" s="83"/>
-      <c r="F4" s="83"/>
-      <c r="G4" s="83"/>
-      <c r="H4" s="83"/>
-      <c r="I4" s="84"/>
+      <c r="D4" s="79"/>
+      <c r="E4" s="80"/>
+      <c r="F4" s="80"/>
+      <c r="G4" s="80"/>
+      <c r="H4" s="80"/>
+      <c r="I4" s="81"/>
     </row>
     <row r="5" spans="2:9">
       <c r="B5" s="22"/>
-      <c r="D5" s="82"/>
-      <c r="E5" s="83"/>
-      <c r="F5" s="83"/>
-      <c r="G5" s="83"/>
-      <c r="H5" s="83"/>
-      <c r="I5" s="84"/>
+      <c r="D5" s="79"/>
+      <c r="E5" s="80"/>
+      <c r="F5" s="80"/>
+      <c r="G5" s="80"/>
+      <c r="H5" s="80"/>
+      <c r="I5" s="81"/>
     </row>
     <row r="6" spans="2:9" ht="15.75" thickBot="1">
-      <c r="D6" s="85"/>
-      <c r="E6" s="86"/>
-      <c r="F6" s="86"/>
-      <c r="G6" s="86"/>
-      <c r="H6" s="86"/>
-      <c r="I6" s="87"/>
+      <c r="D6" s="82"/>
+      <c r="E6" s="83"/>
+      <c r="F6" s="83"/>
+      <c r="G6" s="83"/>
+      <c r="H6" s="83"/>
+      <c r="I6" s="84"/>
     </row>
     <row r="7" spans="2:9" ht="15.75" thickBot="1"/>
     <row r="8" spans="2:9" ht="19.5" thickBot="1">
@@ -2931,20 +2937,20 @@
   <sheetData>
     <row r="1" spans="2:14" ht="15.75" thickBot="1"/>
     <row r="2" spans="2:14" ht="31.5" customHeight="1" thickBot="1">
-      <c r="B2" s="67" t="s">
+      <c r="B2" s="64" t="s">
         <v>99</v>
       </c>
-      <c r="C2" s="68" t="s">
+      <c r="C2" s="65" t="s">
         <v>87</v>
       </c>
-      <c r="D2" s="126" t="s">
+      <c r="D2" s="103" t="s">
         <v>7</v>
       </c>
-      <c r="E2" s="127"/>
-      <c r="F2" s="206" t="s">
+      <c r="E2" s="104"/>
+      <c r="F2" s="127" t="s">
         <v>19</v>
       </c>
-      <c r="G2" s="207"/>
+      <c r="G2" s="128"/>
       <c r="H2"/>
       <c r="I2"/>
     </row>
@@ -2953,7 +2959,7 @@
       <c r="C3" s="2"/>
       <c r="D3"/>
       <c r="E3"/>
-      <c r="H3" s="64"/>
+      <c r="H3" s="61"/>
       <c r="I3"/>
     </row>
     <row r="4" spans="2:14" ht="15.75" thickBot="1">
@@ -2965,20 +2971,20 @@
       <c r="I4"/>
     </row>
     <row r="5" spans="2:14" ht="16.5" thickTop="1">
-      <c r="B5" s="148" t="s">
+      <c r="B5" s="125" t="s">
         <v>8</v>
       </c>
-      <c r="C5" s="149"/>
-      <c r="D5" s="42"/>
-      <c r="E5" s="43">
+      <c r="C5" s="126"/>
+      <c r="D5" s="41"/>
+      <c r="E5" s="42">
         <v>15</v>
       </c>
-      <c r="F5" s="134" t="s">
+      <c r="F5" s="111" t="s">
         <v>89</v>
       </c>
-      <c r="G5" s="135"/>
-      <c r="H5" s="44"/>
-      <c r="I5" s="39"/>
+      <c r="G5" s="112"/>
+      <c r="H5" s="41"/>
+      <c r="I5" s="38"/>
     </row>
     <row r="6" spans="2:14" ht="15.6" customHeight="1">
       <c r="B6" s="3" t="s">
@@ -2987,21 +2993,21 @@
       <c r="C6" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="D6" s="42"/>
-      <c r="E6" s="45">
+      <c r="D6" s="41"/>
+      <c r="E6" s="43">
         <v>15</v>
       </c>
-      <c r="F6" s="136" t="s">
+      <c r="F6" s="113" t="s">
         <v>90</v>
       </c>
-      <c r="G6" s="137"/>
-      <c r="H6" s="46"/>
-      <c r="I6" s="40"/>
-      <c r="J6" s="58"/>
-      <c r="K6" s="58"/>
-      <c r="L6" s="58"/>
-      <c r="M6" s="58"/>
-      <c r="N6" s="58"/>
+      <c r="G6" s="114"/>
+      <c r="H6" s="44"/>
+      <c r="I6" s="39"/>
+      <c r="J6" s="38"/>
+      <c r="K6" s="38"/>
+      <c r="L6" s="38"/>
+      <c r="M6" s="38"/>
+      <c r="N6" s="38"/>
     </row>
     <row r="7" spans="2:14" ht="16.149999999999999" customHeight="1">
       <c r="B7" s="5" t="s">
@@ -3010,21 +3016,21 @@
       <c r="C7" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="D7" s="42"/>
-      <c r="E7" s="47">
+      <c r="D7" s="41"/>
+      <c r="E7" s="45">
         <v>16</v>
       </c>
-      <c r="F7" s="138" t="s">
+      <c r="F7" s="115" t="s">
         <v>91</v>
       </c>
-      <c r="G7" s="139"/>
-      <c r="H7" s="44"/>
-      <c r="I7" s="39"/>
-      <c r="J7" s="58"/>
-      <c r="K7" s="58"/>
-      <c r="L7" s="58"/>
-      <c r="M7" s="58"/>
-      <c r="N7" s="58"/>
+      <c r="G7" s="116"/>
+      <c r="H7" s="41"/>
+      <c r="I7" s="38"/>
+      <c r="J7" s="38"/>
+      <c r="K7" s="38"/>
+      <c r="L7" s="38"/>
+      <c r="M7" s="38"/>
+      <c r="N7" s="38"/>
     </row>
     <row r="8" spans="2:14" ht="16.5" thickBot="1">
       <c r="B8" s="7" t="s">
@@ -3033,21 +3039,21 @@
       <c r="C8" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="D8" s="42"/>
-      <c r="E8" s="48">
+      <c r="D8" s="41"/>
+      <c r="E8" s="46">
         <v>16</v>
       </c>
-      <c r="F8" s="140" t="s">
+      <c r="F8" s="117" t="s">
         <v>92</v>
       </c>
-      <c r="G8" s="141"/>
-      <c r="H8" s="46"/>
-      <c r="I8" s="40"/>
-      <c r="J8" s="58"/>
-      <c r="K8" s="58"/>
-      <c r="L8" s="58"/>
-      <c r="M8" s="58"/>
-      <c r="N8" s="58"/>
+      <c r="G8" s="118"/>
+      <c r="H8" s="44"/>
+      <c r="I8" s="39"/>
+      <c r="J8" s="38"/>
+      <c r="K8" s="38"/>
+      <c r="L8" s="38"/>
+      <c r="M8" s="38"/>
+      <c r="N8" s="38"/>
     </row>
     <row r="9" spans="2:14" ht="18" customHeight="1" thickBot="1">
       <c r="B9" s="8" t="s">
@@ -3056,17 +3062,17 @@
       <c r="C9" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="D9" s="42"/>
-      <c r="E9" s="42"/>
-      <c r="F9" s="42"/>
-      <c r="G9" s="42"/>
-      <c r="H9" s="49"/>
-      <c r="I9" s="57"/>
-      <c r="J9" s="58"/>
-      <c r="K9" s="58"/>
-      <c r="L9" s="58"/>
-      <c r="M9" s="58"/>
-      <c r="N9" s="58"/>
+      <c r="D9" s="41"/>
+      <c r="E9" s="41"/>
+      <c r="F9" s="41"/>
+      <c r="G9" s="41"/>
+      <c r="H9" s="47"/>
+      <c r="I9" s="55"/>
+      <c r="J9" s="38"/>
+      <c r="K9" s="38"/>
+      <c r="L9" s="38"/>
+      <c r="M9" s="38"/>
+      <c r="N9" s="38"/>
     </row>
     <row r="10" spans="2:14" ht="16.5" thickBot="1">
       <c r="B10" s="9" t="s">
@@ -3075,562 +3081,571 @@
       <c r="C10" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="D10" s="42"/>
-      <c r="E10" s="42"/>
-      <c r="F10" s="91" t="s">
+      <c r="D10" s="41"/>
+      <c r="E10" s="41"/>
+      <c r="F10" s="143" t="s">
         <v>98</v>
       </c>
-      <c r="G10" s="92"/>
-      <c r="H10" s="49"/>
-      <c r="I10" s="57"/>
-      <c r="J10" s="58"/>
-      <c r="K10" s="58"/>
-      <c r="L10" s="58"/>
-      <c r="M10" s="58"/>
-      <c r="N10" s="58"/>
+      <c r="G10" s="144"/>
+      <c r="H10" s="47"/>
+      <c r="I10" s="55"/>
+      <c r="J10" s="38"/>
+      <c r="K10" s="38"/>
+      <c r="L10" s="38"/>
+      <c r="M10" s="38"/>
+      <c r="N10" s="38"/>
     </row>
     <row r="11" spans="2:14" ht="16.5" thickTop="1" thickBot="1">
-      <c r="B11" s="50"/>
-      <c r="C11" s="50"/>
-      <c r="D11" s="50"/>
-      <c r="E11" s="50"/>
-      <c r="F11" s="93"/>
-      <c r="G11" s="94"/>
-      <c r="H11" s="49"/>
-      <c r="I11" s="57"/>
-      <c r="J11" s="58"/>
-      <c r="K11" s="58"/>
-      <c r="L11" s="58"/>
-      <c r="M11" s="58"/>
-      <c r="N11" s="58"/>
+      <c r="B11" s="48"/>
+      <c r="C11" s="48"/>
+      <c r="D11" s="48"/>
+      <c r="E11" s="48"/>
+      <c r="F11" s="145"/>
+      <c r="G11" s="146"/>
+      <c r="H11" s="47"/>
+      <c r="I11" s="55"/>
+      <c r="J11" s="38"/>
+      <c r="K11" s="38"/>
+      <c r="L11" s="38"/>
+      <c r="M11" s="38"/>
+      <c r="N11" s="38"/>
     </row>
     <row r="12" spans="2:14" ht="14.45" customHeight="1" thickBot="1">
-      <c r="B12" s="50"/>
-      <c r="C12" s="142" t="s">
+      <c r="B12" s="48"/>
+      <c r="C12" s="119" t="s">
         <v>88</v>
       </c>
-      <c r="D12" s="143"/>
-      <c r="E12" s="144"/>
-      <c r="F12" s="95"/>
-      <c r="G12" s="96"/>
-      <c r="H12" s="51"/>
-      <c r="I12" s="58"/>
-      <c r="J12" s="58"/>
-      <c r="K12" s="58"/>
-      <c r="L12" s="58"/>
-      <c r="M12" s="58"/>
-      <c r="N12" s="58"/>
+      <c r="D12" s="120"/>
+      <c r="E12" s="121"/>
+      <c r="F12" s="147"/>
+      <c r="G12" s="148"/>
+      <c r="H12" s="49"/>
+      <c r="I12" s="38"/>
+      <c r="J12" s="38"/>
+      <c r="K12" s="38"/>
+      <c r="L12" s="38"/>
+      <c r="M12" s="38"/>
+      <c r="N12" s="38"/>
     </row>
     <row r="13" spans="2:14" ht="15.75" thickBot="1">
-      <c r="B13" s="50"/>
-      <c r="C13" s="145"/>
-      <c r="D13" s="146"/>
-      <c r="E13" s="147"/>
-      <c r="F13" s="151" t="s">
+      <c r="B13" s="48"/>
+      <c r="C13" s="122"/>
+      <c r="D13" s="123"/>
+      <c r="E13" s="124"/>
+      <c r="F13" s="138" t="s">
         <v>22</v>
       </c>
-      <c r="G13" s="151"/>
-      <c r="H13" s="152"/>
-      <c r="I13" s="58"/>
-      <c r="J13" s="59"/>
-      <c r="K13" s="58"/>
-      <c r="L13" s="58"/>
-      <c r="M13" s="58"/>
-      <c r="N13" s="58"/>
+      <c r="G13" s="138"/>
+      <c r="H13" s="139"/>
+      <c r="I13" s="38"/>
+      <c r="J13" s="56"/>
+      <c r="K13" s="38"/>
+      <c r="L13" s="38"/>
+      <c r="M13" s="38"/>
+      <c r="N13" s="38"/>
     </row>
     <row r="14" spans="2:14" ht="16.899999999999999" customHeight="1" thickBot="1">
-      <c r="B14" s="97" t="s">
+      <c r="B14" s="129" t="s">
         <v>23</v>
       </c>
-      <c r="C14" s="98"/>
-      <c r="D14" s="98"/>
-      <c r="E14" s="118"/>
-      <c r="F14" s="153"/>
-      <c r="G14" s="154"/>
-      <c r="H14" s="155"/>
-      <c r="I14" s="58"/>
-      <c r="J14" s="58"/>
-      <c r="K14" s="58"/>
-      <c r="L14" s="58"/>
-      <c r="M14" s="58"/>
-      <c r="N14" s="58"/>
+      <c r="C14" s="130"/>
+      <c r="D14" s="130"/>
+      <c r="E14" s="131"/>
+      <c r="F14" s="140"/>
+      <c r="G14" s="141"/>
+      <c r="H14" s="142"/>
+      <c r="I14" s="38"/>
+      <c r="J14" s="38"/>
+      <c r="K14" s="38"/>
+      <c r="L14" s="38"/>
+      <c r="M14" s="38"/>
+      <c r="N14" s="38"/>
     </row>
     <row r="15" spans="2:14">
-      <c r="B15" s="99"/>
-      <c r="C15" s="100"/>
-      <c r="D15" s="100"/>
-      <c r="E15" s="150"/>
-      <c r="F15" s="130" t="s">
+      <c r="B15" s="132"/>
+      <c r="C15" s="133"/>
+      <c r="D15" s="133"/>
+      <c r="E15" s="134"/>
+      <c r="F15" s="107" t="s">
         <v>24</v>
       </c>
-      <c r="G15" s="132" t="s">
+      <c r="G15" s="109" t="s">
         <v>25</v>
       </c>
-      <c r="H15" s="128" t="s">
+      <c r="H15" s="105" t="s">
         <v>26</v>
       </c>
-      <c r="I15" s="115"/>
-      <c r="J15" s="58"/>
-      <c r="K15" s="58"/>
-      <c r="L15" s="58"/>
-      <c r="M15" s="58"/>
-      <c r="N15" s="58"/>
+      <c r="I15" s="152"/>
+      <c r="J15" s="38"/>
+      <c r="K15" s="38"/>
+      <c r="L15" s="38"/>
+      <c r="M15" s="38"/>
+      <c r="N15" s="38"/>
     </row>
     <row r="16" spans="2:14" ht="30.75" customHeight="1" thickBot="1">
-      <c r="B16" s="101"/>
-      <c r="C16" s="102"/>
-      <c r="D16" s="102"/>
-      <c r="E16" s="119"/>
-      <c r="F16" s="131"/>
-      <c r="G16" s="133"/>
-      <c r="H16" s="129"/>
-      <c r="I16" s="115"/>
-      <c r="J16" s="58"/>
-      <c r="K16" s="58"/>
-      <c r="L16" s="58"/>
-      <c r="M16" s="58"/>
-      <c r="N16" s="58"/>
+      <c r="B16" s="135"/>
+      <c r="C16" s="136"/>
+      <c r="D16" s="136"/>
+      <c r="E16" s="137"/>
+      <c r="F16" s="108"/>
+      <c r="G16" s="110"/>
+      <c r="H16" s="106"/>
+      <c r="I16" s="152"/>
+      <c r="J16" s="38"/>
+      <c r="K16" s="38"/>
+      <c r="L16" s="38"/>
+      <c r="M16" s="38"/>
+      <c r="N16" s="38"/>
     </row>
     <row r="17" spans="2:14" ht="29.1" customHeight="1" thickBot="1">
-      <c r="B17" s="97" t="str">
+      <c r="B17" s="129" t="str">
         <f>IF(C2="Your Name Here!", "Enter your name in C2 and your very own problem will appear here:)","Compute the final value of an account into which you make a one time deposite of  $"&amp;Random!J19&amp;" and leave the money for "&amp;Random!J20&amp;" years at an APR of "&amp;Random!J21&amp;"% with simple interest. Compute the interest earned.")</f>
         <v>Enter your name in C2 and your very own problem will appear here:)</v>
       </c>
-      <c r="C17" s="98"/>
-      <c r="D17" s="98"/>
-      <c r="E17" s="118"/>
-      <c r="F17" s="120"/>
-      <c r="G17" s="123" t="s">
+      <c r="C17" s="130"/>
+      <c r="D17" s="130"/>
+      <c r="E17" s="131"/>
+      <c r="F17" s="155"/>
+      <c r="G17" s="91" t="s">
         <v>27</v>
       </c>
-      <c r="H17" s="52" t="s">
+      <c r="H17" s="50" t="s">
         <v>28</v>
       </c>
-      <c r="I17" s="55" t="s">
+      <c r="I17" s="53" t="s">
         <v>29</v>
       </c>
-      <c r="J17" s="66"/>
-      <c r="K17" s="58"/>
-      <c r="L17" s="58"/>
-      <c r="M17" s="58"/>
-      <c r="N17" s="58"/>
+      <c r="J17" s="63"/>
+      <c r="K17" s="38"/>
+      <c r="L17" s="38"/>
+      <c r="M17" s="38"/>
+      <c r="N17" s="38"/>
     </row>
     <row r="18" spans="2:14" ht="35.25" customHeight="1" thickBot="1">
-      <c r="B18" s="101"/>
-      <c r="C18" s="102"/>
-      <c r="D18" s="102"/>
-      <c r="E18" s="119"/>
-      <c r="F18" s="121"/>
-      <c r="G18" s="124"/>
-      <c r="H18" s="112"/>
-      <c r="I18" s="109"/>
-      <c r="J18" s="66"/>
-      <c r="K18" s="58"/>
-      <c r="L18" s="58"/>
-      <c r="M18" s="58"/>
-      <c r="N18" s="58"/>
+      <c r="B18" s="135"/>
+      <c r="C18" s="136"/>
+      <c r="D18" s="136"/>
+      <c r="E18" s="137"/>
+      <c r="F18" s="156"/>
+      <c r="G18" s="92"/>
+      <c r="H18" s="94"/>
+      <c r="I18" s="97"/>
+      <c r="J18" s="63"/>
+      <c r="K18" s="38"/>
+      <c r="L18" s="38"/>
+      <c r="M18" s="38"/>
+      <c r="N18" s="38"/>
     </row>
     <row r="19" spans="2:14" ht="18" customHeight="1">
-      <c r="B19" s="69" t="s">
+      <c r="B19" s="66" t="s">
         <v>30</v>
       </c>
-      <c r="C19" s="65" t="s">
+      <c r="C19" s="62" t="s">
         <v>31</v>
       </c>
-      <c r="D19" s="65" t="s">
-        <v>32</v>
-      </c>
-      <c r="E19" s="65" t="s">
+      <c r="D19" s="205"/>
+      <c r="E19" s="62" t="s">
         <v>33</v>
       </c>
-      <c r="F19" s="121"/>
-      <c r="G19" s="124"/>
-      <c r="H19" s="113"/>
-      <c r="I19" s="110"/>
-      <c r="J19" s="66"/>
-      <c r="K19" s="58"/>
-      <c r="L19" s="58"/>
-      <c r="M19" s="58"/>
-      <c r="N19" s="58"/>
+      <c r="F19" s="156"/>
+      <c r="G19" s="92"/>
+      <c r="H19" s="95"/>
+      <c r="I19" s="98"/>
+      <c r="J19" s="63"/>
+      <c r="K19" s="38"/>
+      <c r="L19" s="38"/>
+      <c r="M19" s="38"/>
+      <c r="N19" s="38"/>
     </row>
     <row r="20" spans="2:14" ht="18" customHeight="1" thickBot="1">
-      <c r="B20" s="72"/>
-      <c r="C20" s="73"/>
-      <c r="D20" s="74"/>
-      <c r="E20" s="74"/>
-      <c r="F20" s="122"/>
-      <c r="G20" s="125"/>
-      <c r="H20" s="114"/>
-      <c r="I20" s="111"/>
-      <c r="J20" s="66"/>
-      <c r="K20" s="58"/>
-      <c r="L20" s="58"/>
-      <c r="M20" s="58"/>
-      <c r="N20" s="58"/>
+      <c r="B20" s="69"/>
+      <c r="C20" s="70"/>
+      <c r="D20" s="206"/>
+      <c r="E20" s="71"/>
+      <c r="F20" s="157"/>
+      <c r="G20" s="93"/>
+      <c r="H20" s="96"/>
+      <c r="I20" s="99"/>
+      <c r="J20" s="63"/>
+      <c r="K20" s="38"/>
+      <c r="L20" s="38"/>
+      <c r="M20" s="38"/>
+      <c r="N20" s="38"/>
     </row>
     <row r="21" spans="2:14" ht="29.1" customHeight="1" thickBot="1">
-      <c r="B21" s="97" t="str">
+      <c r="B21" s="129" t="str">
         <f>IF(C2="Your Name Here!", "Enter your name in C2 and your very own problem will appear here:)","Compute the final value of an account into which you make a one time deposite of  $"&amp;Random!J19&amp;" and leave the money for "&amp;Random!J20&amp;" years at an APR of "&amp;Random!J21&amp;"% with compounded monthly. Compute the interest earned.")</f>
         <v>Enter your name in C2 and your very own problem will appear here:)</v>
       </c>
-      <c r="C21" s="98"/>
-      <c r="D21" s="98"/>
-      <c r="E21" s="116"/>
-      <c r="F21" s="156"/>
-      <c r="G21" s="123" t="s">
+      <c r="C21" s="130"/>
+      <c r="D21" s="130"/>
+      <c r="E21" s="153"/>
+      <c r="F21" s="88"/>
+      <c r="G21" s="91" t="s">
         <v>34</v>
       </c>
-      <c r="H21" s="53" t="s">
+      <c r="H21" s="51" t="s">
         <v>28</v>
       </c>
-      <c r="I21" s="54" t="s">
+      <c r="I21" s="52" t="s">
         <v>29</v>
       </c>
-      <c r="J21" s="60"/>
-      <c r="K21" s="61"/>
-      <c r="L21" s="58"/>
-      <c r="M21" s="58"/>
-      <c r="N21" s="58"/>
+      <c r="J21" s="57"/>
+      <c r="K21" s="58"/>
+      <c r="L21" s="38"/>
+      <c r="M21" s="38"/>
+      <c r="N21" s="38"/>
     </row>
     <row r="22" spans="2:14" ht="36.75" customHeight="1" thickBot="1">
-      <c r="B22" s="101"/>
-      <c r="C22" s="102"/>
-      <c r="D22" s="102"/>
-      <c r="E22" s="117"/>
-      <c r="F22" s="157"/>
-      <c r="G22" s="124"/>
-      <c r="H22" s="109"/>
-      <c r="I22" s="112"/>
-      <c r="J22" s="60"/>
-      <c r="K22" s="61"/>
-      <c r="L22" s="58"/>
-      <c r="M22" s="58"/>
-      <c r="N22" s="58"/>
+      <c r="B22" s="135"/>
+      <c r="C22" s="136"/>
+      <c r="D22" s="136"/>
+      <c r="E22" s="154"/>
+      <c r="F22" s="89"/>
+      <c r="G22" s="92"/>
+      <c r="H22" s="97"/>
+      <c r="I22" s="94"/>
+      <c r="J22" s="57"/>
+      <c r="K22" s="58"/>
+      <c r="L22" s="38"/>
+      <c r="M22" s="38"/>
+      <c r="N22" s="38"/>
     </row>
     <row r="23" spans="2:14" ht="18" customHeight="1">
-      <c r="B23" s="69" t="s">
+      <c r="B23" s="66" t="s">
         <v>30</v>
       </c>
-      <c r="C23" s="65" t="s">
+      <c r="C23" s="62" t="s">
         <v>31</v>
       </c>
-      <c r="D23" s="65" t="s">
+      <c r="D23" s="62" t="s">
         <v>32</v>
       </c>
-      <c r="E23" s="65" t="s">
+      <c r="E23" s="62" t="s">
         <v>33</v>
       </c>
-      <c r="F23" s="157"/>
-      <c r="G23" s="124"/>
-      <c r="H23" s="110"/>
-      <c r="I23" s="113"/>
-      <c r="J23" s="60"/>
-      <c r="K23" s="61"/>
-      <c r="L23" s="58"/>
-      <c r="M23" s="58"/>
-      <c r="N23" s="58"/>
+      <c r="F23" s="89"/>
+      <c r="G23" s="92"/>
+      <c r="H23" s="98"/>
+      <c r="I23" s="95"/>
+      <c r="J23" s="57"/>
+      <c r="K23" s="58"/>
+      <c r="L23" s="38"/>
+      <c r="M23" s="38"/>
+      <c r="N23" s="38"/>
     </row>
     <row r="24" spans="2:14" ht="18" customHeight="1" thickBot="1">
-      <c r="B24" s="72"/>
-      <c r="C24" s="73"/>
-      <c r="D24" s="74"/>
-      <c r="E24" s="74"/>
-      <c r="F24" s="158"/>
-      <c r="G24" s="125"/>
-      <c r="H24" s="111"/>
-      <c r="I24" s="114"/>
-      <c r="J24" s="60"/>
-      <c r="K24" s="61"/>
-      <c r="L24" s="58"/>
-      <c r="M24" s="58"/>
-      <c r="N24" s="58"/>
+      <c r="B24" s="69"/>
+      <c r="C24" s="70"/>
+      <c r="D24" s="71"/>
+      <c r="E24" s="71"/>
+      <c r="F24" s="90"/>
+      <c r="G24" s="93"/>
+      <c r="H24" s="99"/>
+      <c r="I24" s="96"/>
+      <c r="J24" s="57"/>
+      <c r="K24" s="58"/>
+      <c r="L24" s="38"/>
+      <c r="M24" s="38"/>
+      <c r="N24" s="38"/>
     </row>
     <row r="25" spans="2:14" ht="29.1" customHeight="1" thickBot="1">
-      <c r="B25" s="97" t="str">
+      <c r="B25" s="129" t="str">
         <f>IF(C2="Your Name Here!", "Enter your name in C2 and your very own problem will appear here:)","Compute the final value of an account into which you put  $"&amp;Random!I19&amp;" monthly for "&amp;Random!J20&amp;" years at an APR of "&amp;Random!J21&amp;"% compounded monthly. Compute the total invested and the interest earned.")</f>
         <v>Enter your name in C2 and your very own problem will appear here:)</v>
       </c>
-      <c r="C25" s="98"/>
-      <c r="D25" s="98"/>
-      <c r="E25" s="98"/>
-      <c r="F25" s="103"/>
-      <c r="G25" s="106" t="s">
+      <c r="C25" s="130"/>
+      <c r="D25" s="130"/>
+      <c r="E25" s="130"/>
+      <c r="F25" s="85"/>
+      <c r="G25" s="149" t="s">
         <v>35</v>
       </c>
-      <c r="H25" s="55" t="s">
+      <c r="H25" s="53" t="s">
         <v>28</v>
       </c>
-      <c r="I25" s="54" t="s">
+      <c r="I25" s="52" t="s">
         <v>36</v>
       </c>
-      <c r="J25" s="56" t="s">
+      <c r="J25" s="54" t="s">
         <v>37</v>
       </c>
-      <c r="K25" s="61"/>
-      <c r="L25" s="58"/>
-      <c r="M25" s="58"/>
-      <c r="N25" s="58"/>
+      <c r="K25" s="58"/>
+      <c r="L25" s="38"/>
+      <c r="M25" s="38"/>
+      <c r="N25" s="38"/>
     </row>
     <row r="26" spans="2:14" ht="18" customHeight="1">
-      <c r="B26" s="99"/>
-      <c r="C26" s="100"/>
-      <c r="D26" s="100"/>
-      <c r="E26" s="100"/>
-      <c r="F26" s="104"/>
-      <c r="G26" s="107"/>
-      <c r="H26" s="109"/>
-      <c r="I26" s="112"/>
-      <c r="J26" s="88"/>
-      <c r="K26" s="61"/>
-      <c r="L26" s="58"/>
-      <c r="M26" s="58"/>
-      <c r="N26" s="58"/>
+      <c r="B26" s="132"/>
+      <c r="C26" s="133"/>
+      <c r="D26" s="133"/>
+      <c r="E26" s="133"/>
+      <c r="F26" s="86"/>
+      <c r="G26" s="150"/>
+      <c r="H26" s="97"/>
+      <c r="I26" s="94"/>
+      <c r="J26" s="100"/>
+      <c r="K26" s="58"/>
+      <c r="L26" s="38"/>
+      <c r="M26" s="38"/>
+      <c r="N26" s="38"/>
     </row>
     <row r="27" spans="2:14" ht="18" customHeight="1" thickBot="1">
-      <c r="B27" s="101"/>
-      <c r="C27" s="102"/>
-      <c r="D27" s="102"/>
-      <c r="E27" s="102"/>
-      <c r="F27" s="104"/>
-      <c r="G27" s="107"/>
-      <c r="H27" s="110"/>
-      <c r="I27" s="113"/>
-      <c r="J27" s="89"/>
-      <c r="K27" s="61"/>
-      <c r="L27" s="58"/>
-      <c r="M27" s="58"/>
-      <c r="N27" s="58"/>
+      <c r="B27" s="135"/>
+      <c r="C27" s="136"/>
+      <c r="D27" s="136"/>
+      <c r="E27" s="136"/>
+      <c r="F27" s="86"/>
+      <c r="G27" s="150"/>
+      <c r="H27" s="98"/>
+      <c r="I27" s="95"/>
+      <c r="J27" s="101"/>
+      <c r="K27" s="58"/>
+      <c r="L27" s="38"/>
+      <c r="M27" s="38"/>
+      <c r="N27" s="38"/>
     </row>
     <row r="28" spans="2:14" ht="18" customHeight="1">
-      <c r="B28" s="69" t="s">
+      <c r="B28" s="66" t="s">
         <v>30</v>
       </c>
-      <c r="C28" s="65" t="s">
+      <c r="C28" s="62" t="s">
         <v>31</v>
       </c>
-      <c r="D28" s="65" t="s">
+      <c r="D28" s="62" t="s">
         <v>32</v>
       </c>
-      <c r="E28" s="70" t="s">
+      <c r="E28" s="67" t="s">
         <v>33</v>
       </c>
-      <c r="F28" s="104"/>
-      <c r="G28" s="107"/>
-      <c r="H28" s="110"/>
-      <c r="I28" s="113"/>
-      <c r="J28" s="89"/>
-      <c r="K28" s="58"/>
-      <c r="L28" s="58"/>
-      <c r="M28" s="58"/>
-      <c r="N28" s="58"/>
+      <c r="F28" s="86"/>
+      <c r="G28" s="150"/>
+      <c r="H28" s="98"/>
+      <c r="I28" s="95"/>
+      <c r="J28" s="101"/>
+      <c r="K28" s="38"/>
+      <c r="L28" s="38"/>
+      <c r="M28" s="38"/>
+      <c r="N28" s="38"/>
     </row>
     <row r="29" spans="2:14" ht="18" customHeight="1" thickBot="1">
-      <c r="B29" s="72"/>
-      <c r="C29" s="73"/>
-      <c r="D29" s="74"/>
-      <c r="E29" s="74"/>
-      <c r="F29" s="105"/>
-      <c r="G29" s="108"/>
-      <c r="H29" s="111"/>
-      <c r="I29" s="114"/>
-      <c r="J29" s="90"/>
-      <c r="K29" s="58"/>
-      <c r="L29" s="58"/>
-      <c r="M29" s="58"/>
-      <c r="N29" s="58"/>
+      <c r="B29" s="69"/>
+      <c r="C29" s="70"/>
+      <c r="D29" s="71"/>
+      <c r="E29" s="71"/>
+      <c r="F29" s="87"/>
+      <c r="G29" s="151"/>
+      <c r="H29" s="99"/>
+      <c r="I29" s="96"/>
+      <c r="J29" s="102"/>
+      <c r="K29" s="38"/>
+      <c r="L29" s="38"/>
+      <c r="M29" s="38"/>
+      <c r="N29" s="38"/>
     </row>
     <row r="30" spans="2:14" ht="29.1" customHeight="1" thickBot="1">
-      <c r="B30" s="97" t="str">
+      <c r="B30" s="129" t="str">
         <f>IF(C2="Your Name Here!", "Enter your name in C2 and your very own problem will appear here:)","Compute the monthly payment (P) required to reach a future amount (FV) of $"&amp;Solutions!J22&amp;".00 after "&amp;Random!J20&amp;" years at an APR of "&amp;Random!J21&amp;"% compounded monthly. Compute the total invested and the interest earned.")</f>
         <v>Enter your name in C2 and your very own problem will appear here:)</v>
       </c>
-      <c r="C30" s="98"/>
-      <c r="D30" s="98"/>
-      <c r="E30" s="98"/>
-      <c r="F30" s="103"/>
-      <c r="G30" s="106" t="s">
+      <c r="C30" s="130"/>
+      <c r="D30" s="130"/>
+      <c r="E30" s="130"/>
+      <c r="F30" s="85"/>
+      <c r="G30" s="149" t="s">
         <v>95</v>
       </c>
-      <c r="H30" s="55" t="s">
+      <c r="H30" s="53" t="s">
         <v>96</v>
       </c>
-      <c r="I30" s="54" t="s">
+      <c r="I30" s="52" t="s">
         <v>36</v>
       </c>
-      <c r="J30" s="56" t="s">
+      <c r="J30" s="54" t="s">
         <v>37</v>
       </c>
-      <c r="K30" s="58"/>
-      <c r="L30" s="58"/>
-      <c r="M30" s="58"/>
-      <c r="N30" s="58"/>
+      <c r="K30" s="38"/>
+      <c r="L30" s="38"/>
+      <c r="M30" s="38"/>
+      <c r="N30" s="38"/>
     </row>
     <row r="31" spans="2:14" ht="18" customHeight="1">
-      <c r="B31" s="99"/>
-      <c r="C31" s="100"/>
-      <c r="D31" s="100"/>
-      <c r="E31" s="100"/>
-      <c r="F31" s="104"/>
-      <c r="G31" s="107"/>
-      <c r="H31" s="109"/>
-      <c r="I31" s="112"/>
-      <c r="J31" s="88"/>
-      <c r="K31" s="58"/>
-      <c r="L31" s="58"/>
-      <c r="M31" s="58"/>
-      <c r="N31" s="58"/>
+      <c r="B31" s="132"/>
+      <c r="C31" s="133"/>
+      <c r="D31" s="133"/>
+      <c r="E31" s="133"/>
+      <c r="F31" s="86"/>
+      <c r="G31" s="150"/>
+      <c r="H31" s="97"/>
+      <c r="I31" s="94"/>
+      <c r="J31" s="100"/>
+      <c r="K31" s="38"/>
+      <c r="L31" s="38"/>
+      <c r="M31" s="38"/>
+      <c r="N31" s="38"/>
     </row>
     <row r="32" spans="2:14" ht="18" customHeight="1" thickBot="1">
-      <c r="B32" s="101"/>
-      <c r="C32" s="102"/>
-      <c r="D32" s="102"/>
-      <c r="E32" s="102"/>
-      <c r="F32" s="104"/>
-      <c r="G32" s="107"/>
-      <c r="H32" s="110"/>
-      <c r="I32" s="113"/>
-      <c r="J32" s="89"/>
-      <c r="K32" s="58"/>
-      <c r="L32" s="58"/>
-      <c r="M32" s="58"/>
-      <c r="N32" s="58"/>
+      <c r="B32" s="135"/>
+      <c r="C32" s="136"/>
+      <c r="D32" s="136"/>
+      <c r="E32" s="136"/>
+      <c r="F32" s="86"/>
+      <c r="G32" s="150"/>
+      <c r="H32" s="98"/>
+      <c r="I32" s="95"/>
+      <c r="J32" s="101"/>
+      <c r="K32" s="38"/>
+      <c r="L32" s="38"/>
+      <c r="M32" s="38"/>
+      <c r="N32" s="38"/>
     </row>
     <row r="33" spans="2:14" ht="18" customHeight="1">
-      <c r="B33" s="69" t="s">
+      <c r="B33" s="66" t="s">
         <v>93</v>
       </c>
-      <c r="C33" s="65" t="s">
+      <c r="C33" s="62" t="s">
         <v>31</v>
       </c>
-      <c r="D33" s="65" t="s">
+      <c r="D33" s="62" t="s">
         <v>32</v>
       </c>
-      <c r="E33" s="71" t="s">
+      <c r="E33" s="68" t="s">
         <v>33</v>
       </c>
-      <c r="F33" s="104"/>
-      <c r="G33" s="107"/>
-      <c r="H33" s="110"/>
-      <c r="I33" s="113"/>
-      <c r="J33" s="89"/>
-      <c r="K33" s="58"/>
-      <c r="L33" s="58"/>
-      <c r="M33" s="58"/>
-      <c r="N33" s="58"/>
+      <c r="F33" s="86"/>
+      <c r="G33" s="150"/>
+      <c r="H33" s="98"/>
+      <c r="I33" s="95"/>
+      <c r="J33" s="101"/>
+      <c r="K33" s="38"/>
+      <c r="L33" s="38"/>
+      <c r="M33" s="38"/>
+      <c r="N33" s="38"/>
     </row>
     <row r="34" spans="2:14" ht="18" customHeight="1" thickBot="1">
-      <c r="B34" s="75"/>
-      <c r="C34" s="76"/>
-      <c r="D34" s="77"/>
-      <c r="E34" s="78"/>
-      <c r="F34" s="105"/>
-      <c r="G34" s="108"/>
-      <c r="H34" s="111"/>
-      <c r="I34" s="114"/>
-      <c r="J34" s="90"/>
-      <c r="K34" s="58"/>
-      <c r="L34" s="58"/>
-      <c r="M34" s="58"/>
-      <c r="N34" s="58"/>
+      <c r="B34" s="72"/>
+      <c r="C34" s="73"/>
+      <c r="D34" s="74"/>
+      <c r="E34" s="75"/>
+      <c r="F34" s="87"/>
+      <c r="G34" s="151"/>
+      <c r="H34" s="99"/>
+      <c r="I34" s="96"/>
+      <c r="J34" s="102"/>
+      <c r="K34" s="38"/>
+      <c r="L34" s="38"/>
+      <c r="M34" s="38"/>
+      <c r="N34" s="38"/>
     </row>
     <row r="35" spans="2:14">
-      <c r="B35" s="62"/>
-      <c r="C35" s="62"/>
-      <c r="D35" s="62"/>
-      <c r="E35" s="62"/>
-      <c r="F35" s="58"/>
-      <c r="G35" s="58"/>
-      <c r="H35" s="63"/>
-      <c r="I35" s="57"/>
-      <c r="J35" s="58"/>
-      <c r="K35" s="58"/>
-      <c r="L35" s="58"/>
-      <c r="M35" s="58"/>
-      <c r="N35" s="58"/>
+      <c r="B35" s="59"/>
+      <c r="C35" s="59"/>
+      <c r="D35" s="59"/>
+      <c r="E35" s="59"/>
+      <c r="F35" s="38"/>
+      <c r="G35" s="38"/>
+      <c r="H35" s="60"/>
+      <c r="I35" s="55"/>
+      <c r="J35" s="38"/>
+      <c r="K35" s="38"/>
+      <c r="L35" s="38"/>
+      <c r="M35" s="38"/>
+      <c r="N35" s="38"/>
     </row>
     <row r="36" spans="2:14">
-      <c r="B36" s="62"/>
-      <c r="C36" s="62"/>
-      <c r="D36" s="62"/>
-      <c r="E36" s="62"/>
-      <c r="F36" s="58"/>
-      <c r="G36" s="58"/>
-      <c r="H36" s="63"/>
-      <c r="I36" s="57"/>
-      <c r="J36" s="58"/>
-      <c r="K36" s="58"/>
-      <c r="L36" s="58"/>
-      <c r="M36" s="58"/>
-      <c r="N36" s="58"/>
+      <c r="B36" s="59"/>
+      <c r="C36" s="59"/>
+      <c r="D36" s="59"/>
+      <c r="E36" s="59"/>
+      <c r="F36" s="38"/>
+      <c r="G36" s="38"/>
+      <c r="H36" s="60"/>
+      <c r="I36" s="55"/>
+      <c r="J36" s="38"/>
+      <c r="K36" s="38"/>
+      <c r="L36" s="38"/>
+      <c r="M36" s="38"/>
+      <c r="N36" s="38"/>
     </row>
     <row r="37" spans="2:14">
-      <c r="B37" s="62"/>
-      <c r="C37" s="62"/>
-      <c r="D37" s="62"/>
-      <c r="E37" s="62"/>
-      <c r="F37" s="58"/>
-      <c r="G37" s="58"/>
-      <c r="H37" s="63"/>
-      <c r="I37" s="57"/>
-      <c r="J37" s="58"/>
-      <c r="K37" s="58"/>
-      <c r="L37" s="58"/>
-      <c r="M37" s="58"/>
-      <c r="N37" s="58"/>
+      <c r="B37" s="59"/>
+      <c r="C37" s="59"/>
+      <c r="D37" s="59"/>
+      <c r="E37" s="59"/>
+      <c r="F37" s="38"/>
+      <c r="G37" s="38"/>
+      <c r="H37" s="60"/>
+      <c r="I37" s="55"/>
+      <c r="J37" s="38"/>
+      <c r="K37" s="38"/>
+      <c r="L37" s="38"/>
+      <c r="M37" s="38"/>
+      <c r="N37" s="38"/>
     </row>
     <row r="38" spans="2:14">
-      <c r="B38" s="62"/>
-      <c r="C38" s="62"/>
-      <c r="D38" s="62"/>
-      <c r="E38" s="62"/>
-      <c r="F38" s="58"/>
-      <c r="G38" s="58"/>
-      <c r="H38" s="63"/>
-      <c r="I38" s="57"/>
-      <c r="J38" s="58"/>
-      <c r="K38" s="58"/>
-      <c r="L38" s="58"/>
-      <c r="M38" s="58"/>
-      <c r="N38" s="58"/>
+      <c r="B38" s="59"/>
+      <c r="C38" s="59"/>
+      <c r="D38" s="59"/>
+      <c r="E38" s="59"/>
+      <c r="F38" s="38"/>
+      <c r="G38" s="38"/>
+      <c r="H38" s="60"/>
+      <c r="I38" s="55"/>
+      <c r="J38" s="38"/>
+      <c r="K38" s="38"/>
+      <c r="L38" s="38"/>
+      <c r="M38" s="38"/>
+      <c r="N38" s="38"/>
     </row>
     <row r="39" spans="2:14">
-      <c r="B39" s="62"/>
-      <c r="C39" s="62"/>
-      <c r="D39" s="62"/>
-      <c r="E39" s="62"/>
-      <c r="F39" s="58"/>
-      <c r="G39" s="58"/>
-      <c r="H39" s="63"/>
-      <c r="I39" s="57"/>
-      <c r="J39" s="58"/>
-      <c r="K39" s="58"/>
-      <c r="L39" s="58"/>
-      <c r="M39" s="58"/>
-      <c r="N39" s="58"/>
+      <c r="B39" s="59"/>
+      <c r="C39" s="59"/>
+      <c r="D39" s="59"/>
+      <c r="E39" s="59"/>
+      <c r="F39" s="38"/>
+      <c r="G39" s="38"/>
+      <c r="H39" s="60"/>
+      <c r="I39" s="55"/>
+      <c r="J39" s="38"/>
+      <c r="K39" s="38"/>
+      <c r="L39" s="38"/>
+      <c r="M39" s="38"/>
+      <c r="N39" s="38"/>
     </row>
     <row r="40" spans="2:14">
-      <c r="B40" s="62"/>
-      <c r="C40" s="62"/>
-      <c r="D40" s="62"/>
-      <c r="E40" s="62"/>
-      <c r="F40" s="58"/>
-      <c r="G40" s="58"/>
-      <c r="H40" s="63"/>
-      <c r="I40" s="57"/>
-      <c r="J40" s="58"/>
-      <c r="K40" s="58"/>
-      <c r="L40" s="58"/>
-      <c r="M40" s="58"/>
-      <c r="N40" s="58"/>
+      <c r="B40" s="59"/>
+      <c r="C40" s="59"/>
+      <c r="D40" s="59"/>
+      <c r="E40" s="59"/>
+      <c r="F40" s="38"/>
+      <c r="G40" s="38"/>
+      <c r="H40" s="60"/>
+      <c r="I40" s="55"/>
+      <c r="J40" s="38"/>
+      <c r="K40" s="38"/>
+      <c r="L40" s="38"/>
+      <c r="M40" s="38"/>
+      <c r="N40" s="38"/>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="HBUmoshzQfujUApxiZOkmxr64phh4MabnD8OKjUO3K98CxY+zIl71v3ZiTGeuhMvZHrOlYhT2/GiSVuW0qoHaw==" saltValue="wNldlurn4DywqFAzkh+ebQ==" spinCount="100000" sheet="1" scenarios="1" formatCells="0" formatColumns="0" formatRows="0"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="EDfkFGfGpT7bt3IsMtyhDwurN2gJEPSXH0GZECX8LKhKq9+SpKwcNVPG3sOOyZGGqUzYZLDYf8RV2gvSJmPsfg==" saltValue="Hga5ACUo6exJi4Vas5wqBQ==" spinCount="100000" sheet="1" scenarios="1" formatCells="0" formatColumns="0" formatRows="0"/>
   <mergeCells count="37">
-    <mergeCell ref="F25:F29"/>
-    <mergeCell ref="F21:F24"/>
-    <mergeCell ref="G21:G24"/>
-    <mergeCell ref="H18:H20"/>
-    <mergeCell ref="I18:I20"/>
+    <mergeCell ref="J31:J34"/>
+    <mergeCell ref="F10:G12"/>
+    <mergeCell ref="B30:E32"/>
+    <mergeCell ref="F30:F34"/>
+    <mergeCell ref="G30:G34"/>
+    <mergeCell ref="H31:H34"/>
+    <mergeCell ref="I31:I34"/>
+    <mergeCell ref="B25:E27"/>
+    <mergeCell ref="I15:I16"/>
+    <mergeCell ref="B21:E22"/>
+    <mergeCell ref="B17:E18"/>
+    <mergeCell ref="G25:G29"/>
+    <mergeCell ref="H26:H29"/>
+    <mergeCell ref="I26:I29"/>
+    <mergeCell ref="F17:F20"/>
+    <mergeCell ref="G17:G20"/>
     <mergeCell ref="J26:J29"/>
     <mergeCell ref="H22:H24"/>
     <mergeCell ref="I22:I24"/>
@@ -3647,22 +3662,11 @@
     <mergeCell ref="F2:G2"/>
     <mergeCell ref="B14:E16"/>
     <mergeCell ref="F13:H14"/>
-    <mergeCell ref="J31:J34"/>
-    <mergeCell ref="F10:G12"/>
-    <mergeCell ref="B30:E32"/>
-    <mergeCell ref="F30:F34"/>
-    <mergeCell ref="G30:G34"/>
-    <mergeCell ref="H31:H34"/>
-    <mergeCell ref="I31:I34"/>
-    <mergeCell ref="B25:E27"/>
-    <mergeCell ref="I15:I16"/>
-    <mergeCell ref="B21:E22"/>
-    <mergeCell ref="B17:E18"/>
-    <mergeCell ref="G25:G29"/>
-    <mergeCell ref="H26:H29"/>
-    <mergeCell ref="I26:I29"/>
-    <mergeCell ref="F17:F20"/>
-    <mergeCell ref="G17:G20"/>
+    <mergeCell ref="F25:F29"/>
+    <mergeCell ref="F21:F24"/>
+    <mergeCell ref="G21:G24"/>
+    <mergeCell ref="H18:H20"/>
+    <mergeCell ref="I18:I20"/>
   </mergeCells>
   <conditionalFormatting sqref="H18:I20 H22:I24 H26:J29">
     <cfRule type="expression" dxfId="8" priority="10" stopIfTrue="1">
@@ -3735,6 +3739,172 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9572B328-54A0-4480-98DA-E056F557FEA7}">
+  <dimension ref="A1:M21"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="9.140625" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13">
+      <c r="A1" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="B1" t="s">
+        <v>101</v>
+      </c>
+      <c r="C1" s="59">
+        <v>1</v>
+      </c>
+      <c r="D1" t="str">
+        <f>Financial!C2</f>
+        <v>Your Name Here!</v>
+      </c>
+      <c r="F1" s="158" t="str">
+        <f ca="1">IF(M1="ACTIVE", "✓ Tracking Active", "⚠️ ERROR: Enable Iterative Calculations (File &gt; Options &gt; Formulas)")</f>
+        <v>✓ Tracking Active</v>
+      </c>
+      <c r="G1" s="158"/>
+      <c r="H1" s="158"/>
+      <c r="I1" s="158"/>
+      <c r="J1" s="158"/>
+      <c r="K1" s="158"/>
+      <c r="L1" s="158"/>
+      <c r="M1" s="1" t="str">
+        <f ca="1">IF(M1="ACTIVE", "ACTIVE", "ACTIVE")</f>
+        <v>ACTIVE</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13">
+      <c r="A2" s="1" t="str">
+        <f t="shared" ref="A2:A19" ca="1" si="0">IF(D$1&lt;&gt;A3,A3,A2)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="3" spans="1:13">
+      <c r="A3" s="1" t="str">
+        <f t="shared" ca="1" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="4" spans="1:13">
+      <c r="A4" s="1" t="str">
+        <f t="shared" ca="1" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="5" spans="1:13">
+      <c r="A5" s="1" t="str">
+        <f t="shared" ca="1" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="6" spans="1:13">
+      <c r="A6" s="1" t="str">
+        <f t="shared" ca="1" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="7" spans="1:13">
+      <c r="A7" s="1" t="str">
+        <f t="shared" ca="1" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="8" spans="1:13">
+      <c r="A8" s="1" t="str">
+        <f t="shared" ca="1" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="9" spans="1:13">
+      <c r="A9" s="1" t="str">
+        <f t="shared" ca="1" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="10" spans="1:13">
+      <c r="A10" s="1" t="str">
+        <f t="shared" ca="1" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="11" spans="1:13">
+      <c r="A11" s="1" t="str">
+        <f t="shared" ca="1" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="12" spans="1:13">
+      <c r="A12" s="1" t="str">
+        <f t="shared" ca="1" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="13" spans="1:13">
+      <c r="A13" s="1" t="str">
+        <f t="shared" ca="1" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="14" spans="1:13">
+      <c r="A14" s="1" t="str">
+        <f t="shared" ca="1" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="15" spans="1:13">
+      <c r="A15" s="1" t="str">
+        <f t="shared" ca="1" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="16" spans="1:13">
+      <c r="A16" s="1" t="str">
+        <f t="shared" ca="1" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="17" spans="1:1">
+      <c r="A17" s="1" t="str">
+        <f t="shared" ca="1" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="18" spans="1:1">
+      <c r="A18" s="1" t="str">
+        <f t="shared" ca="1" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="19" spans="1:1">
+      <c r="A19" s="1" t="str">
+        <f t="shared" ca="1" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="20" spans="1:1">
+      <c r="A20" s="1" t="str">
+        <f ca="1">IF(D$1&lt;&gt;A21,A21,A20)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21" spans="1:1">
+      <c r="A21" s="1" t="str">
+        <f ca="1">IF(C1="","",IF(D$1&lt;&gt;A21,D$1,A21))</f>
+        <v>Your Name Here!</v>
+      </c>
+    </row>
+  </sheetData>
+  <sheetProtection algorithmName="SHA-512" hashValue="mDmxsR9/F+KFRQiwQGvNvYcKhpPUbGjhynC9obDVzCU6QTZsXpiaancHpimExcyp1asnVY7CBiXkSb5xPEtRcg==" saltValue="PMw8EghkaxCIjhaDgny43w==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
+  <mergeCells count="1">
+    <mergeCell ref="F1:L1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5D87AA56-18AC-4DC7-BC45-323D5E38D83F}">
   <dimension ref="A1:W55"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -5735,7 +5905,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AE723ACA-9738-4B60-95AB-B3B2AD139FFF}">
   <dimension ref="B2:K34"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -5758,10 +5928,10 @@
       <c r="C2" s="20" t="s">
         <v>83</v>
       </c>
-      <c r="D2" s="194" t="s">
+      <c r="D2" s="159" t="s">
         <v>7</v>
       </c>
-      <c r="E2" s="195"/>
+      <c r="E2" s="158"/>
       <c r="H2"/>
       <c r="I2"/>
     </row>
@@ -5782,10 +5952,10 @@
       <c r="I4"/>
     </row>
     <row r="5" spans="2:9" ht="17.25" thickTop="1" thickBot="1">
-      <c r="B5" s="148" t="s">
+      <c r="B5" s="125" t="s">
         <v>8</v>
       </c>
-      <c r="C5" s="149"/>
+      <c r="C5" s="126"/>
       <c r="D5"/>
       <c r="E5"/>
       <c r="H5"/>
@@ -5799,11 +5969,11 @@
         <v>10</v>
       </c>
       <c r="D6"/>
-      <c r="E6" s="196" t="s">
+      <c r="E6" s="160" t="s">
         <v>11</v>
       </c>
-      <c r="F6" s="197"/>
-      <c r="G6" s="198"/>
+      <c r="F6" s="161"/>
+      <c r="G6" s="162"/>
       <c r="H6"/>
       <c r="I6"/>
     </row>
@@ -5815,11 +5985,11 @@
         <v>13</v>
       </c>
       <c r="D7"/>
-      <c r="E7" s="199" t="s">
+      <c r="E7" s="163" t="s">
         <v>14</v>
       </c>
-      <c r="F7" s="200"/>
-      <c r="G7" s="201"/>
+      <c r="F7" s="164"/>
+      <c r="G7" s="165"/>
       <c r="H7"/>
       <c r="I7"/>
     </row>
@@ -5844,10 +6014,10 @@
       </c>
       <c r="D9"/>
       <c r="E9"/>
-      <c r="F9" s="182" t="s">
+      <c r="F9" s="175" t="s">
         <v>84</v>
       </c>
-      <c r="G9" s="182"/>
+      <c r="G9" s="175"/>
       <c r="H9"/>
       <c r="I9"/>
     </row>
@@ -5870,61 +6040,61 @@
       <c r="I12"/>
     </row>
     <row r="13" spans="2:9" ht="15.75" thickBot="1">
-      <c r="F13" s="183" t="s">
+      <c r="F13" s="176" t="s">
         <v>22</v>
       </c>
-      <c r="G13" s="184"/>
-      <c r="H13" s="184"/>
+      <c r="G13" s="177"/>
+      <c r="H13" s="177"/>
       <c r="I13"/>
     </row>
     <row r="14" spans="2:9" ht="16.899999999999999" customHeight="1" thickBot="1">
-      <c r="B14" s="79" t="s">
+      <c r="B14" s="76" t="s">
         <v>23</v>
       </c>
-      <c r="C14" s="80"/>
-      <c r="D14" s="80"/>
-      <c r="E14" s="81"/>
-      <c r="F14" s="185"/>
-      <c r="G14" s="186"/>
-      <c r="H14" s="186"/>
+      <c r="C14" s="77"/>
+      <c r="D14" s="77"/>
+      <c r="E14" s="78"/>
+      <c r="F14" s="178"/>
+      <c r="G14" s="179"/>
+      <c r="H14" s="179"/>
       <c r="I14"/>
     </row>
     <row r="15" spans="2:9">
-      <c r="B15" s="82"/>
-      <c r="C15" s="83"/>
-      <c r="D15" s="83"/>
-      <c r="E15" s="84"/>
-      <c r="F15" s="187" t="s">
+      <c r="B15" s="79"/>
+      <c r="C15" s="80"/>
+      <c r="D15" s="80"/>
+      <c r="E15" s="81"/>
+      <c r="F15" s="180" t="s">
         <v>24</v>
       </c>
-      <c r="G15" s="189" t="s">
+      <c r="G15" s="182" t="s">
         <v>25</v>
       </c>
-      <c r="H15" s="202" t="s">
+      <c r="H15" s="166" t="s">
         <v>26</v>
       </c>
-      <c r="I15" s="204"/>
+      <c r="I15" s="168"/>
     </row>
     <row r="16" spans="2:9" ht="15.75" thickBot="1">
-      <c r="B16" s="85"/>
-      <c r="C16" s="86"/>
-      <c r="D16" s="86"/>
-      <c r="E16" s="87"/>
-      <c r="F16" s="188"/>
-      <c r="G16" s="190"/>
-      <c r="H16" s="203"/>
-      <c r="I16" s="204"/>
+      <c r="B16" s="82"/>
+      <c r="C16" s="83"/>
+      <c r="D16" s="83"/>
+      <c r="E16" s="84"/>
+      <c r="F16" s="181"/>
+      <c r="G16" s="183"/>
+      <c r="H16" s="167"/>
+      <c r="I16" s="168"/>
     </row>
     <row r="17" spans="2:11" ht="30.75" thickBot="1">
-      <c r="B17" s="79" t="str">
+      <c r="B17" s="76" t="str">
         <f ca="1">IF(C2="Your Name Here!", "Enter your name in C2 and your very own problem will appear here:)","Compute the final value of an account into which you make a one time deposite of  $"&amp;Random!J19&amp;" and leave the money for "&amp;Random!J20&amp;" years at an APR of "&amp;Random!J21&amp;"% with simple interest. Compute the interest earned.")</f>
         <v>Compute the final value of an account into which you make a one time deposite of  $5225 and leave the money for 8 years at an APR of 5.13% with simple interest. Compute the interest earned.</v>
       </c>
-      <c r="C17" s="80"/>
-      <c r="D17" s="80"/>
-      <c r="E17" s="81"/>
-      <c r="F17" s="191"/>
-      <c r="G17" s="179" t="s">
+      <c r="C17" s="77"/>
+      <c r="D17" s="77"/>
+      <c r="E17" s="78"/>
+      <c r="F17" s="184"/>
+      <c r="G17" s="187" t="s">
         <v>27</v>
       </c>
       <c r="H17" s="33" t="s">
@@ -5935,17 +6105,17 @@
       </c>
     </row>
     <row r="18" spans="2:11" ht="34.9" customHeight="1" thickBot="1">
-      <c r="B18" s="85"/>
-      <c r="C18" s="86"/>
-      <c r="D18" s="86"/>
-      <c r="E18" s="87"/>
-      <c r="F18" s="192"/>
-      <c r="G18" s="180"/>
-      <c r="H18" s="171">
+      <c r="B18" s="82"/>
+      <c r="C18" s="83"/>
+      <c r="D18" s="83"/>
+      <c r="E18" s="84"/>
+      <c r="F18" s="185"/>
+      <c r="G18" s="188"/>
+      <c r="H18" s="169">
         <f>Financial!B20*(1+Financial!C20*Financial!E20)</f>
         <v>0</v>
       </c>
-      <c r="I18" s="168">
+      <c r="I18" s="172">
         <f>H18-Financial!B20</f>
         <v>0</v>
       </c>
@@ -5963,10 +6133,10 @@
       <c r="E19" s="12" t="s">
         <v>33</v>
       </c>
-      <c r="F19" s="192"/>
-      <c r="G19" s="180"/>
-      <c r="H19" s="172"/>
-      <c r="I19" s="169"/>
+      <c r="F19" s="185"/>
+      <c r="G19" s="188"/>
+      <c r="H19" s="170"/>
+      <c r="I19" s="173"/>
     </row>
     <row r="20" spans="2:11" ht="15.75" thickBot="1">
       <c r="B20" s="25">
@@ -5984,21 +6154,21 @@
         <f ca="1">Random!J20</f>
         <v>8</v>
       </c>
-      <c r="F20" s="193"/>
-      <c r="G20" s="181"/>
-      <c r="H20" s="173"/>
-      <c r="I20" s="170"/>
+      <c r="F20" s="186"/>
+      <c r="G20" s="189"/>
+      <c r="H20" s="171"/>
+      <c r="I20" s="174"/>
     </row>
     <row r="21" spans="2:11" ht="14.45" customHeight="1" thickBot="1">
-      <c r="B21" s="79" t="str">
+      <c r="B21" s="76" t="str">
         <f ca="1">IF(C2="Your Name Here!", "Enter your name in C2 and your very own problem will appear here:)","Compute the final value of an account into which you make a one time deposite of  $"&amp;Random!J19&amp;" and leave the money for "&amp;Random!J20&amp;" years at an APR of "&amp;Random!J21&amp;"% with compounded monthly. Compute the interest earned.")</f>
         <v>Compute the final value of an account into which you make a one time deposite of  $5225 and leave the money for 8 years at an APR of 5.13% with compounded monthly. Compute the interest earned.</v>
       </c>
-      <c r="C21" s="80"/>
-      <c r="D21" s="80"/>
-      <c r="E21" s="174"/>
-      <c r="F21" s="176"/>
-      <c r="G21" s="179" t="s">
+      <c r="C21" s="77"/>
+      <c r="D21" s="77"/>
+      <c r="E21" s="190"/>
+      <c r="F21" s="192"/>
+      <c r="G21" s="187" t="s">
         <v>34</v>
       </c>
       <c r="H21" s="34" t="s">
@@ -6011,21 +6181,21 @@
       <c r="K21" s="15"/>
     </row>
     <row r="22" spans="2:11" ht="35.450000000000003" customHeight="1" thickBot="1">
-      <c r="B22" s="85"/>
-      <c r="C22" s="86"/>
-      <c r="D22" s="86"/>
-      <c r="E22" s="175"/>
-      <c r="F22" s="177"/>
-      <c r="G22" s="180"/>
-      <c r="H22" s="168" t="e">
+      <c r="B22" s="82"/>
+      <c r="C22" s="83"/>
+      <c r="D22" s="83"/>
+      <c r="E22" s="191"/>
+      <c r="F22" s="193"/>
+      <c r="G22" s="188"/>
+      <c r="H22" s="172" t="e">
         <f>Financial!B24*(1+Financial!C24/Financial!D24)^(Financial!D24*Financial!E24)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="I22" s="171" t="e">
+      <c r="I22" s="169" t="e">
         <f>H22-Financial!B24</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="J22" s="41">
+      <c r="J22" s="40">
         <f ca="1">ROUND(B24*(1+C24/D24)^(D24*E24),0)</f>
         <v>7869</v>
       </c>
@@ -6044,10 +6214,10 @@
       <c r="E23" s="12" t="s">
         <v>33</v>
       </c>
-      <c r="F23" s="177"/>
-      <c r="G23" s="180"/>
-      <c r="H23" s="169"/>
-      <c r="I23" s="172"/>
+      <c r="F23" s="193"/>
+      <c r="G23" s="188"/>
+      <c r="H23" s="173"/>
+      <c r="I23" s="170"/>
       <c r="J23" s="18"/>
       <c r="K23" s="15"/>
     </row>
@@ -6067,23 +6237,23 @@
         <f ca="1">Random!J20</f>
         <v>8</v>
       </c>
-      <c r="F24" s="178"/>
-      <c r="G24" s="181"/>
-      <c r="H24" s="170"/>
-      <c r="I24" s="173"/>
+      <c r="F24" s="194"/>
+      <c r="G24" s="189"/>
+      <c r="H24" s="174"/>
+      <c r="I24" s="171"/>
       <c r="J24" s="18"/>
       <c r="K24" s="15"/>
     </row>
     <row r="25" spans="2:11" ht="14.45" customHeight="1" thickBot="1">
-      <c r="B25" s="79" t="str">
+      <c r="B25" s="76" t="str">
         <f ca="1">IF(C2="Your Name Here!", "Enter your name in C2 and your very own problem will appear here:)","Compute the final value of an account into which you put  $"&amp;Random!I19&amp;" monthly for "&amp;Random!J20&amp;" years at an APR of "&amp;Random!J21&amp;"% compounded monthly. Compute the interest earned.")</f>
         <v>Compute the final value of an account into which you put  $54.43 monthly for 8 years at an APR of 5.13% compounded monthly. Compute the interest earned.</v>
       </c>
-      <c r="C25" s="80"/>
-      <c r="D25" s="80"/>
-      <c r="E25" s="80"/>
-      <c r="F25" s="162"/>
-      <c r="G25" s="165" t="s">
+      <c r="C25" s="77"/>
+      <c r="D25" s="77"/>
+      <c r="E25" s="77"/>
+      <c r="F25" s="198"/>
+      <c r="G25" s="201" t="s">
         <v>35</v>
       </c>
       <c r="H25" s="35" t="s">
@@ -6098,36 +6268,36 @@
       <c r="K25" s="15"/>
     </row>
     <row r="26" spans="2:11">
-      <c r="B26" s="82"/>
-      <c r="C26" s="83"/>
-      <c r="D26" s="83"/>
-      <c r="E26" s="83"/>
-      <c r="F26" s="163"/>
-      <c r="G26" s="166"/>
-      <c r="H26" s="168" t="e">
+      <c r="B26" s="79"/>
+      <c r="C26" s="80"/>
+      <c r="D26" s="80"/>
+      <c r="E26" s="80"/>
+      <c r="F26" s="199"/>
+      <c r="G26" s="202"/>
+      <c r="H26" s="172" t="e">
         <f>Financial!B29*((1+Financial!C29/Financial!D29)^(Financial!D29*Financial!E29)-1)/(Financial!C29/Financial!D29)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="I26" s="171">
+      <c r="I26" s="169">
         <f>Financial!B29*Financial!D29*Financial!E29</f>
         <v>0</v>
       </c>
-      <c r="J26" s="159" t="e">
+      <c r="J26" s="195" t="e">
         <f>H26-I26</f>
         <v>#DIV/0!</v>
       </c>
       <c r="K26" s="15"/>
     </row>
     <row r="27" spans="2:11" ht="19.149999999999999" customHeight="1" thickBot="1">
-      <c r="B27" s="85"/>
-      <c r="C27" s="86"/>
-      <c r="D27" s="86"/>
-      <c r="E27" s="86"/>
-      <c r="F27" s="163"/>
-      <c r="G27" s="166"/>
-      <c r="H27" s="169"/>
-      <c r="I27" s="172"/>
-      <c r="J27" s="160"/>
+      <c r="B27" s="82"/>
+      <c r="C27" s="83"/>
+      <c r="D27" s="83"/>
+      <c r="E27" s="83"/>
+      <c r="F27" s="199"/>
+      <c r="G27" s="202"/>
+      <c r="H27" s="173"/>
+      <c r="I27" s="170"/>
+      <c r="J27" s="196"/>
       <c r="K27" s="15"/>
     </row>
     <row r="28" spans="2:11">
@@ -6143,11 +6313,11 @@
       <c r="E28" s="28" t="s">
         <v>33</v>
       </c>
-      <c r="F28" s="163"/>
-      <c r="G28" s="166"/>
-      <c r="H28" s="169"/>
-      <c r="I28" s="172"/>
-      <c r="J28" s="160"/>
+      <c r="F28" s="199"/>
+      <c r="G28" s="202"/>
+      <c r="H28" s="173"/>
+      <c r="I28" s="170"/>
+      <c r="J28" s="196"/>
     </row>
     <row r="29" spans="2:11" ht="15.75" thickBot="1">
       <c r="B29" s="29">
@@ -6165,22 +6335,22 @@
         <f ca="1">Random!J20</f>
         <v>8</v>
       </c>
-      <c r="F29" s="164"/>
-      <c r="G29" s="167"/>
-      <c r="H29" s="170"/>
-      <c r="I29" s="173"/>
-      <c r="J29" s="161"/>
+      <c r="F29" s="200"/>
+      <c r="G29" s="203"/>
+      <c r="H29" s="174"/>
+      <c r="I29" s="171"/>
+      <c r="J29" s="197"/>
     </row>
     <row r="30" spans="2:11" ht="30.75" thickBot="1">
-      <c r="B30" s="79" t="e">
+      <c r="B30" s="76" t="e">
         <f ca="1">IF(C2="Your Name Here!", "Enter your name in C2 and your very own problem will appear here:)","Compute the monthly payment (P) required to reach a future amount (FV) of $"&amp;ROUND(Solutions!H22,2)&amp;" after "&amp;Random!J20&amp;" years at an APR of "&amp;Random!J21&amp;"% compounded monthly. Compute the total invested and the interest earned.")</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="C30" s="80"/>
-      <c r="D30" s="80"/>
-      <c r="E30" s="80"/>
-      <c r="F30" s="162"/>
-      <c r="G30" s="165" t="s">
+      <c r="C30" s="77"/>
+      <c r="D30" s="77"/>
+      <c r="E30" s="77"/>
+      <c r="F30" s="198"/>
+      <c r="G30" s="201" t="s">
         <v>95</v>
       </c>
       <c r="H30" s="35" t="s">
@@ -6189,40 +6359,40 @@
       <c r="I30" s="37" t="s">
         <v>36</v>
       </c>
-      <c r="J30" s="38" t="s">
+      <c r="J30" s="27" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="31" spans="2:11">
-      <c r="B31" s="82"/>
-      <c r="C31" s="83"/>
-      <c r="D31" s="83"/>
-      <c r="E31" s="83"/>
-      <c r="F31" s="163"/>
-      <c r="G31" s="166"/>
-      <c r="H31" s="168" t="e">
+      <c r="B31" s="79"/>
+      <c r="C31" s="80"/>
+      <c r="D31" s="80"/>
+      <c r="E31" s="80"/>
+      <c r="F31" s="199"/>
+      <c r="G31" s="202"/>
+      <c r="H31" s="172" t="e">
         <f>Financial!B34*(Financial!C34/Financial!D34)/((1+Financial!C34/Financial!D34)^(Financial!D34*Financial!E34)-1)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="I31" s="171" t="e">
+      <c r="I31" s="169" t="e">
         <f>H31*Financial!D34*Financial!E34</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="J31" s="159" t="e">
+      <c r="J31" s="195" t="e">
         <f>Financial!B34-Solutions!I31</f>
         <v>#DIV/0!</v>
       </c>
     </row>
     <row r="32" spans="2:11" ht="15.75" thickBot="1">
-      <c r="B32" s="85"/>
-      <c r="C32" s="86"/>
-      <c r="D32" s="86"/>
-      <c r="E32" s="86"/>
-      <c r="F32" s="163"/>
-      <c r="G32" s="166"/>
-      <c r="H32" s="169"/>
-      <c r="I32" s="172"/>
-      <c r="J32" s="160"/>
+      <c r="B32" s="82"/>
+      <c r="C32" s="83"/>
+      <c r="D32" s="83"/>
+      <c r="E32" s="83"/>
+      <c r="F32" s="199"/>
+      <c r="G32" s="202"/>
+      <c r="H32" s="173"/>
+      <c r="I32" s="170"/>
+      <c r="J32" s="196"/>
     </row>
     <row r="33" spans="2:10">
       <c r="B33" s="11" t="s">
@@ -6237,11 +6407,11 @@
       <c r="E33" s="28" t="s">
         <v>33</v>
       </c>
-      <c r="F33" s="163"/>
-      <c r="G33" s="166"/>
-      <c r="H33" s="169"/>
-      <c r="I33" s="172"/>
-      <c r="J33" s="160"/>
+      <c r="F33" s="199"/>
+      <c r="G33" s="202"/>
+      <c r="H33" s="173"/>
+      <c r="I33" s="170"/>
+      <c r="J33" s="196"/>
     </row>
     <row r="34" spans="2:10" ht="15.75" thickBot="1">
       <c r="B34" s="29">
@@ -6260,20 +6430,32 @@
         <f ca="1">E29</f>
         <v>8</v>
       </c>
-      <c r="F34" s="164"/>
-      <c r="G34" s="167"/>
-      <c r="H34" s="170"/>
-      <c r="I34" s="173"/>
-      <c r="J34" s="161"/>
+      <c r="F34" s="200"/>
+      <c r="G34" s="203"/>
+      <c r="H34" s="174"/>
+      <c r="I34" s="171"/>
+      <c r="J34" s="197"/>
     </row>
   </sheetData>
   <sheetProtection algorithmName="SHA-512" hashValue="0drcGcBptdPjKYjxlrLCv8ldFhFAN9pxyHQIKqb75qpkjn1xDK2YCfnqzKn5wjYb+xD2XBby9mzwjXOH51eGTw==" saltValue="o5me4X/+omJPHU3V7qrs0g==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
   <mergeCells count="33">
-    <mergeCell ref="D2:E2"/>
-    <mergeCell ref="E6:G6"/>
-    <mergeCell ref="E7:G7"/>
-    <mergeCell ref="H15:H16"/>
-    <mergeCell ref="I15:I16"/>
+    <mergeCell ref="J31:J34"/>
+    <mergeCell ref="B30:E32"/>
+    <mergeCell ref="F30:F34"/>
+    <mergeCell ref="G30:G34"/>
+    <mergeCell ref="H31:H34"/>
+    <mergeCell ref="I31:I34"/>
+    <mergeCell ref="J26:J29"/>
+    <mergeCell ref="B25:E27"/>
+    <mergeCell ref="F25:F29"/>
+    <mergeCell ref="G25:G29"/>
+    <mergeCell ref="H26:H29"/>
+    <mergeCell ref="I26:I29"/>
+    <mergeCell ref="B21:E22"/>
+    <mergeCell ref="F21:F24"/>
+    <mergeCell ref="G21:G24"/>
+    <mergeCell ref="H22:H24"/>
+    <mergeCell ref="I22:I24"/>
     <mergeCell ref="H18:H20"/>
     <mergeCell ref="I18:I20"/>
     <mergeCell ref="B5:C5"/>
@@ -6285,23 +6467,11 @@
     <mergeCell ref="B17:E18"/>
     <mergeCell ref="F17:F20"/>
     <mergeCell ref="G17:G20"/>
-    <mergeCell ref="B21:E22"/>
-    <mergeCell ref="F21:F24"/>
-    <mergeCell ref="G21:G24"/>
-    <mergeCell ref="H22:H24"/>
-    <mergeCell ref="I22:I24"/>
-    <mergeCell ref="J26:J29"/>
-    <mergeCell ref="B25:E27"/>
-    <mergeCell ref="F25:F29"/>
-    <mergeCell ref="G25:G29"/>
-    <mergeCell ref="H26:H29"/>
-    <mergeCell ref="I26:I29"/>
-    <mergeCell ref="J31:J34"/>
-    <mergeCell ref="B30:E32"/>
-    <mergeCell ref="F30:F34"/>
-    <mergeCell ref="G30:G34"/>
-    <mergeCell ref="H31:H34"/>
-    <mergeCell ref="I31:I34"/>
+    <mergeCell ref="D2:E2"/>
+    <mergeCell ref="E6:G6"/>
+    <mergeCell ref="E7:G7"/>
+    <mergeCell ref="H15:H16"/>
+    <mergeCell ref="I15:I16"/>
   </mergeCells>
   <conditionalFormatting sqref="H18:I18">
     <cfRule type="expression" dxfId="6" priority="5">
@@ -6340,102 +6510,102 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CB2A50BF-02FC-4EE6-9030-64547612BD39}">
   <dimension ref="B2:H11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="2" spans="2:8">
-      <c r="B2" s="205" t="s">
+      <c r="B2" s="204" t="s">
         <v>85</v>
       </c>
-      <c r="C2" s="205"/>
-      <c r="D2" s="205"/>
-      <c r="E2" s="205"/>
-      <c r="F2" s="205"/>
-      <c r="G2" s="205"/>
-      <c r="H2" s="205"/>
+      <c r="C2" s="204"/>
+      <c r="D2" s="204"/>
+      <c r="E2" s="204"/>
+      <c r="F2" s="204"/>
+      <c r="G2" s="204"/>
+      <c r="H2" s="204"/>
     </row>
     <row r="3" spans="2:8">
-      <c r="B3" s="205"/>
-      <c r="C3" s="205"/>
-      <c r="D3" s="205"/>
-      <c r="E3" s="205"/>
-      <c r="F3" s="205"/>
-      <c r="G3" s="205"/>
-      <c r="H3" s="205"/>
+      <c r="B3" s="204"/>
+      <c r="C3" s="204"/>
+      <c r="D3" s="204"/>
+      <c r="E3" s="204"/>
+      <c r="F3" s="204"/>
+      <c r="G3" s="204"/>
+      <c r="H3" s="204"/>
     </row>
     <row r="4" spans="2:8">
-      <c r="B4" s="205"/>
-      <c r="C4" s="205"/>
-      <c r="D4" s="205"/>
-      <c r="E4" s="205"/>
-      <c r="F4" s="205"/>
-      <c r="G4" s="205"/>
-      <c r="H4" s="205"/>
+      <c r="B4" s="204"/>
+      <c r="C4" s="204"/>
+      <c r="D4" s="204"/>
+      <c r="E4" s="204"/>
+      <c r="F4" s="204"/>
+      <c r="G4" s="204"/>
+      <c r="H4" s="204"/>
     </row>
     <row r="5" spans="2:8">
-      <c r="B5" s="205"/>
-      <c r="C5" s="205"/>
-      <c r="D5" s="205"/>
-      <c r="E5" s="205"/>
-      <c r="F5" s="205"/>
-      <c r="G5" s="205"/>
-      <c r="H5" s="205"/>
+      <c r="B5" s="204"/>
+      <c r="C5" s="204"/>
+      <c r="D5" s="204"/>
+      <c r="E5" s="204"/>
+      <c r="F5" s="204"/>
+      <c r="G5" s="204"/>
+      <c r="H5" s="204"/>
     </row>
     <row r="6" spans="2:8">
-      <c r="B6" s="205"/>
-      <c r="C6" s="205"/>
-      <c r="D6" s="205"/>
-      <c r="E6" s="205"/>
-      <c r="F6" s="205"/>
-      <c r="G6" s="205"/>
-      <c r="H6" s="205"/>
+      <c r="B6" s="204"/>
+      <c r="C6" s="204"/>
+      <c r="D6" s="204"/>
+      <c r="E6" s="204"/>
+      <c r="F6" s="204"/>
+      <c r="G6" s="204"/>
+      <c r="H6" s="204"/>
     </row>
     <row r="7" spans="2:8">
-      <c r="B7" s="205"/>
-      <c r="C7" s="205"/>
-      <c r="D7" s="205"/>
-      <c r="E7" s="205"/>
-      <c r="F7" s="205"/>
-      <c r="G7" s="205"/>
-      <c r="H7" s="205"/>
+      <c r="B7" s="204"/>
+      <c r="C7" s="204"/>
+      <c r="D7" s="204"/>
+      <c r="E7" s="204"/>
+      <c r="F7" s="204"/>
+      <c r="G7" s="204"/>
+      <c r="H7" s="204"/>
     </row>
     <row r="8" spans="2:8">
-      <c r="B8" s="205"/>
-      <c r="C8" s="205"/>
-      <c r="D8" s="205"/>
-      <c r="E8" s="205"/>
-      <c r="F8" s="205"/>
-      <c r="G8" s="205"/>
-      <c r="H8" s="205"/>
+      <c r="B8" s="204"/>
+      <c r="C8" s="204"/>
+      <c r="D8" s="204"/>
+      <c r="E8" s="204"/>
+      <c r="F8" s="204"/>
+      <c r="G8" s="204"/>
+      <c r="H8" s="204"/>
     </row>
     <row r="9" spans="2:8">
-      <c r="B9" s="205"/>
-      <c r="C9" s="205"/>
-      <c r="D9" s="205"/>
-      <c r="E9" s="205"/>
-      <c r="F9" s="205"/>
-      <c r="G9" s="205"/>
-      <c r="H9" s="205"/>
+      <c r="B9" s="204"/>
+      <c r="C9" s="204"/>
+      <c r="D9" s="204"/>
+      <c r="E9" s="204"/>
+      <c r="F9" s="204"/>
+      <c r="G9" s="204"/>
+      <c r="H9" s="204"/>
     </row>
     <row r="10" spans="2:8">
-      <c r="B10" s="205"/>
-      <c r="C10" s="205"/>
-      <c r="D10" s="205"/>
-      <c r="E10" s="205"/>
-      <c r="F10" s="205"/>
-      <c r="G10" s="205"/>
-      <c r="H10" s="205"/>
+      <c r="B10" s="204"/>
+      <c r="C10" s="204"/>
+      <c r="D10" s="204"/>
+      <c r="E10" s="204"/>
+      <c r="F10" s="204"/>
+      <c r="G10" s="204"/>
+      <c r="H10" s="204"/>
     </row>
     <row r="11" spans="2:8">
-      <c r="B11" s="205"/>
-      <c r="C11" s="205"/>
-      <c r="D11" s="205"/>
-      <c r="E11" s="205"/>
-      <c r="F11" s="205"/>
-      <c r="G11" s="205"/>
-      <c r="H11" s="205"/>
+      <c r="B11" s="204"/>
+      <c r="C11" s="204"/>
+      <c r="D11" s="204"/>
+      <c r="E11" s="204"/>
+      <c r="F11" s="204"/>
+      <c r="G11" s="204"/>
+      <c r="H11" s="204"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -6446,6 +6616,25 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="cca9fd2d-ef84-45c9-8063-8f4bd4c29606">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101002C289946819CFF499E91D197BC975371" ma:contentTypeVersion="13" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="674b7a4e239a9748c7aaa97e309327a4">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="cca9fd2d-ef84-45c9-8063-8f4bd4c29606" xmlns:ns3="18557d39-01b8-4d71-9479-3fad465290ae" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="600253478e594d1349e02792803dc53a" ns2:_="" ns3:_="">
     <xsd:import namespace="cca9fd2d-ef84-45c9-8063-8f4bd4c29606"/>
@@ -6662,26 +6851,25 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="cca9fd2d-ef84-45c9-8063-8f4bd4c29606">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B72C8343-FD67-49E2-BAD6-A975045FBBED}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{318A24C3-90E3-418A-8A86-1647DBF244A0}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="cca9fd2d-ef84-45c9-8063-8f4bd4c29606"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3428D67A-ACE8-4C76-8511-B437250C88C3}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -6698,22 +6886,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{318A24C3-90E3-418A-8A86-1647DBF244A0}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="cca9fd2d-ef84-45c9-8063-8f4bd4c29606"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B72C8343-FD67-49E2-BAD6-A975045FBBED}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>